--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1G.1103</t>
+          <t>10.1103</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Iloluky</t>
+          <t>Nclky</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GIRIALCIEI</t>
+          <t>BNACK</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G19H</t>
+          <t>G19A</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -748,6 +748,9 @@
       <c r="J9" t="n">
         <v>8</v>
       </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nclky</t>
+          <t>Rocry</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BNACK</t>
+          <t>GRACE</t>
         </is>
       </c>
     </row>
@@ -703,10 +703,10 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>3345</v>
+        <v>0.317655</v>
       </c>
       <c r="K4" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
@@ -746,10 +746,10 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rocry</t>
+          <t>ROCRY</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.317655</v>
+        <v>31765</v>
       </c>
       <c r="K4" t="n">
         <v>121</v>
@@ -746,9 +746,6 @@
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
         <v>4</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_58927.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
